--- a/data/hardtail/Panorama Taiga EXP 2 2025.xlsx
+++ b/data/hardtail/Panorama Taiga EXP 2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249EEB1C-5319-ED44-A9AF-D416D10890D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7B5B5-8361-2748-B97D-3D0C198ED444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10300" yWindow="6220" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4020" yWindow="3000" windowWidth="24780" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1228,8 +1228,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="1">
-        <f>2.8*25.4</f>
-        <v>71.11999999999999</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
